--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{989F9A6F-868A-4D6F-8D2D-3B6EC2F3EDEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC47CC10-42CE-4FEA-B2DF-B2A4CFD7CA4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1584" yWindow="8808" windowWidth="17952" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17952" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -341,30 +348,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1">
-        <v>10</v>
-      </c>
-      <c r="B1">
-        <v>5</v>
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>9</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>2</v>
       </c>
     </row>
